--- a/artfynd/A 38333-2024 artfynd.xlsx
+++ b/artfynd/A 38333-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121152520</v>
+        <v>121152529</v>
       </c>
       <c r="B2" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>15</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>834695</v>
+        <v>834635</v>
       </c>
       <c r="R2" t="n">
-        <v>7343010</v>
+        <v>7343100</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -789,7 +789,7 @@
         <v>121152532</v>
       </c>
       <c r="B3" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121152529</v>
+        <v>121152533</v>
       </c>
       <c r="B4" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -941,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>834635</v>
+        <v>834650</v>
       </c>
       <c r="R4" t="n">
-        <v>7343100</v>
+        <v>7343090</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121152533</v>
+        <v>121152520</v>
       </c>
       <c r="B5" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>50</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1052,10 +1052,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>834650</v>
+        <v>834695</v>
       </c>
       <c r="R5" t="n">
-        <v>7343090</v>
+        <v>7343010</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1119,10 +1119,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121152527</v>
+        <v>121152528</v>
       </c>
       <c r="B6" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>834715</v>
+        <v>834690</v>
       </c>
       <c r="R6" t="n">
-        <v>7342910</v>
+        <v>7342980</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1230,10 +1230,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121152528</v>
+        <v>121152527</v>
       </c>
       <c r="B7" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1274,10 +1274,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>834690</v>
+        <v>834715</v>
       </c>
       <c r="R7" t="n">
-        <v>7342980</v>
+        <v>7342910</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>

--- a/artfynd/A 38333-2024 artfynd.xlsx
+++ b/artfynd/A 38333-2024 artfynd.xlsx
@@ -786,7 +786,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121152532</v>
+        <v>121152533</v>
       </c>
       <c r="B3" t="n">
         <v>98081</v>
@@ -821,7 +821,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>15</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -830,7 +830,7 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>834651</v>
+        <v>834650</v>
       </c>
       <c r="R3" t="n">
         <v>7343090</v>
@@ -897,7 +897,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121152533</v>
+        <v>121152532</v>
       </c>
       <c r="B4" t="n">
         <v>98081</v>
@@ -932,7 +932,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -941,7 +941,7 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>834650</v>
+        <v>834651</v>
       </c>
       <c r="R4" t="n">
         <v>7343090</v>
@@ -1008,7 +1008,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121152520</v>
+        <v>121152527</v>
       </c>
       <c r="B5" t="n">
         <v>98081</v>
@@ -1043,7 +1043,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1052,10 +1052,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>834695</v>
+        <v>834715</v>
       </c>
       <c r="R5" t="n">
-        <v>7343010</v>
+        <v>7342910</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1119,7 +1119,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121152528</v>
+        <v>121152520</v>
       </c>
       <c r="B6" t="n">
         <v>98081</v>
@@ -1154,7 +1154,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>50</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>834690</v>
+        <v>834695</v>
       </c>
       <c r="R6" t="n">
-        <v>7342980</v>
+        <v>7343010</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1230,7 +1230,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121152527</v>
+        <v>121152528</v>
       </c>
       <c r="B7" t="n">
         <v>98081</v>
@@ -1274,10 +1274,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>834715</v>
+        <v>834690</v>
       </c>
       <c r="R7" t="n">
-        <v>7342910</v>
+        <v>7342980</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>

--- a/artfynd/A 38333-2024 artfynd.xlsx
+++ b/artfynd/A 38333-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121152529</v>
+        <v>121152532</v>
       </c>
       <c r="B2" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>834635</v>
+        <v>834651</v>
       </c>
       <c r="R2" t="n">
-        <v>7343100</v>
+        <v>7343090</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121152533</v>
+        <v>121152520</v>
       </c>
       <c r="B3" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -821,7 +821,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>50</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>834650</v>
+        <v>834695</v>
       </c>
       <c r="R3" t="n">
-        <v>7343090</v>
+        <v>7343010</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121152532</v>
+        <v>121152529</v>
       </c>
       <c r="B4" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -932,7 +932,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>15</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -941,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>834651</v>
+        <v>834635</v>
       </c>
       <c r="R4" t="n">
-        <v>7343090</v>
+        <v>7343100</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121152527</v>
+        <v>121152528</v>
       </c>
       <c r="B5" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1052,10 +1052,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>834715</v>
+        <v>834690</v>
       </c>
       <c r="R5" t="n">
-        <v>7342910</v>
+        <v>7342980</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1119,10 +1119,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121152520</v>
+        <v>121152533</v>
       </c>
       <c r="B6" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1154,7 +1154,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>15</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>834695</v>
+        <v>834650</v>
       </c>
       <c r="R6" t="n">
-        <v>7343010</v>
+        <v>7343090</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1230,10 +1230,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121152528</v>
+        <v>121152527</v>
       </c>
       <c r="B7" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1274,10 +1274,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>834690</v>
+        <v>834715</v>
       </c>
       <c r="R7" t="n">
-        <v>7342980</v>
+        <v>7342910</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>

--- a/artfynd/A 38333-2024 artfynd.xlsx
+++ b/artfynd/A 38333-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121152532</v>
+        <v>121152520</v>
       </c>
       <c r="B2" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>50</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>834651</v>
+        <v>834695</v>
       </c>
       <c r="R2" t="n">
-        <v>7343090</v>
+        <v>7343010</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121152520</v>
+        <v>121152533</v>
       </c>
       <c r="B3" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -821,7 +821,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>15</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>834695</v>
+        <v>834650</v>
       </c>
       <c r="R3" t="n">
-        <v>7343010</v>
+        <v>7343090</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121152529</v>
+        <v>121152532</v>
       </c>
       <c r="B4" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -932,7 +932,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -941,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>834635</v>
+        <v>834651</v>
       </c>
       <c r="R4" t="n">
-        <v>7343100</v>
+        <v>7343090</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1011,7 +1011,7 @@
         <v>121152528</v>
       </c>
       <c r="B5" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1119,10 +1119,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121152533</v>
+        <v>121152527</v>
       </c>
       <c r="B6" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1154,7 +1154,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>834650</v>
+        <v>834715</v>
       </c>
       <c r="R6" t="n">
-        <v>7343090</v>
+        <v>7342910</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1230,10 +1230,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121152527</v>
+        <v>121152529</v>
       </c>
       <c r="B7" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1265,7 +1265,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>15</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1274,10 +1274,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>834715</v>
+        <v>834635</v>
       </c>
       <c r="R7" t="n">
-        <v>7342910</v>
+        <v>7343100</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>

--- a/artfynd/A 38333-2024 artfynd.xlsx
+++ b/artfynd/A 38333-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121152520</v>
+        <v>121152528</v>
       </c>
       <c r="B2" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>834695</v>
+        <v>834690</v>
       </c>
       <c r="R2" t="n">
-        <v>7343010</v>
+        <v>7342980</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121152533</v>
+        <v>121152520</v>
       </c>
       <c r="B3" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -821,7 +821,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>50</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>834650</v>
+        <v>834695</v>
       </c>
       <c r="R3" t="n">
-        <v>7343090</v>
+        <v>7343010</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121152532</v>
+        <v>121152527</v>
       </c>
       <c r="B4" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -932,7 +932,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -941,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>834651</v>
+        <v>834715</v>
       </c>
       <c r="R4" t="n">
-        <v>7343090</v>
+        <v>7342910</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121152528</v>
+        <v>121152533</v>
       </c>
       <c r="B5" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>15</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1052,10 +1052,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>834690</v>
+        <v>834650</v>
       </c>
       <c r="R5" t="n">
-        <v>7342980</v>
+        <v>7343090</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1119,10 +1119,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121152527</v>
+        <v>121152529</v>
       </c>
       <c r="B6" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1154,7 +1154,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>15</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>834715</v>
+        <v>834635</v>
       </c>
       <c r="R6" t="n">
-        <v>7342910</v>
+        <v>7343100</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1230,10 +1230,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121152529</v>
+        <v>121152532</v>
       </c>
       <c r="B7" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1265,7 +1265,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1274,10 +1274,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>834635</v>
+        <v>834651</v>
       </c>
       <c r="R7" t="n">
-        <v>7343100</v>
+        <v>7343090</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>

--- a/artfynd/A 38333-2024 artfynd.xlsx
+++ b/artfynd/A 38333-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121152528</v>
+        <v>121152533</v>
       </c>
       <c r="B2" t="n">
         <v>98098</v>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>15</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>834690</v>
+        <v>834650</v>
       </c>
       <c r="R2" t="n">
-        <v>7342980</v>
+        <v>7343090</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -786,7 +786,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121152520</v>
+        <v>121152532</v>
       </c>
       <c r="B3" t="n">
         <v>98098</v>
@@ -821,7 +821,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>834695</v>
+        <v>834651</v>
       </c>
       <c r="R3" t="n">
-        <v>7343010</v>
+        <v>7343090</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -1008,7 +1008,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121152533</v>
+        <v>121152529</v>
       </c>
       <c r="B5" t="n">
         <v>98098</v>
@@ -1052,10 +1052,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>834650</v>
+        <v>834635</v>
       </c>
       <c r="R5" t="n">
-        <v>7343090</v>
+        <v>7343100</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1119,7 +1119,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121152529</v>
+        <v>121152520</v>
       </c>
       <c r="B6" t="n">
         <v>98098</v>
@@ -1154,7 +1154,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>50</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>834635</v>
+        <v>834695</v>
       </c>
       <c r="R6" t="n">
-        <v>7343100</v>
+        <v>7343010</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1230,7 +1230,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121152532</v>
+        <v>121152528</v>
       </c>
       <c r="B7" t="n">
         <v>98098</v>
@@ -1265,7 +1265,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1274,10 +1274,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>834651</v>
+        <v>834690</v>
       </c>
       <c r="R7" t="n">
-        <v>7343090</v>
+        <v>7342980</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>

--- a/artfynd/A 38333-2024 artfynd.xlsx
+++ b/artfynd/A 38333-2024 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121152533</v>
+        <v>121152520</v>
       </c>
       <c r="B2" t="n">
-        <v>98098</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -710,7 +705,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>50</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -719,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>834650</v>
+        <v>834695</v>
       </c>
       <c r="R2" t="n">
-        <v>7343090</v>
+        <v>7343010</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -786,15 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121152532</v>
+        <v>121152527</v>
       </c>
       <c r="B3" t="n">
-        <v>98098</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -821,7 +811,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -830,10 +820,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>834651</v>
+        <v>834715</v>
       </c>
       <c r="R3" t="n">
-        <v>7343090</v>
+        <v>7342910</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -897,15 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121152527</v>
+        <v>121152528</v>
       </c>
       <c r="B4" t="n">
-        <v>98098</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -941,10 +926,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>834715</v>
+        <v>834690</v>
       </c>
       <c r="R4" t="n">
-        <v>7342910</v>
+        <v>7342980</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1011,12 +996,7 @@
         <v>121152529</v>
       </c>
       <c r="B5" t="n">
-        <v>98098</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1119,15 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121152520</v>
+        <v>121152532</v>
       </c>
       <c r="B6" t="n">
-        <v>98098</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1154,7 +1129,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1163,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>834695</v>
+        <v>834651</v>
       </c>
       <c r="R6" t="n">
-        <v>7343010</v>
+        <v>7343090</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1230,15 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121152528</v>
+        <v>121152533</v>
       </c>
       <c r="B7" t="n">
-        <v>98098</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1265,7 +1235,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>15</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1274,10 +1244,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>834690</v>
+        <v>834650</v>
       </c>
       <c r="R7" t="n">
-        <v>7342980</v>
+        <v>7343090</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>

--- a/artfynd/A 38333-2024 artfynd.xlsx
+++ b/artfynd/A 38333-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121152520</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,6 +894,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121152527</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -990,6 +1005,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121152528</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1096,6 +1116,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121152529</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1202,6 +1227,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121152532</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1308,8 +1338,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121152533</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>